--- a/public/templates/forms/A-029-PolicyReviewApprovalLog-FORM.xlsx
+++ b/public/templates/forms/A-029-PolicyReviewApprovalLog-FORM.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="0"/>
   <fonts count="11">
     <font>
-      <name val="Calibri"/>
+      <name val="Aptos"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -302,7 +302,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -336,7 +336,7 @@
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>

--- a/public/templates/forms/A-029-PolicyReviewApprovalLog-FORM.xlsx
+++ b/public/templates/forms/A-029-PolicyReviewApprovalLog-FORM.xlsx
@@ -4,20 +4,22 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Log" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="11">
     <font>
       <name val="Aptos"/>
@@ -132,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -181,6 +183,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -546,7 +551,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -738,7 +743,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
+    <row r="12" ht="34.7" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
           <t>0001</t>
@@ -950,7 +955,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="19.5" customHeight="1">
+    <row r="29" ht="50.5" customHeight="1">
       <c r="A29" s="9" t="inlineStr">
         <is>
           <t>[Reviewed by (role)]</t>
@@ -960,7 +965,7 @@
       <c r="C29" s="9" t="n"/>
       <c r="D29" s="9" t="n"/>
     </row>
-    <row r="30" ht="19.5" customHeight="1">
+    <row r="30" ht="50.5" customHeight="1">
       <c r="A30" s="9" t="inlineStr">
         <is>
           <t>[Approved by (role)]</t>
@@ -1110,7 +1115,14 @@
     <mergeCell ref="A27:J27"/>
     <mergeCell ref="A33:J33"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <dataValidations count="1">
+    <dataValidation sqref="H12:H21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Outcome" prompt="Select a value" type="list">
+      <formula1>"Reaffirmed,Revised"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -1118,7 +1130,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1143,7 +1155,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1">
+    <row r="3" ht="34.7" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Placeholder key:  [BRACKETED] = fill in   ·   « » = guidance to delete.  Classification, review notes, sign-off, retention, source authority and revision history live on the Log tab.</t>
@@ -1284,13 +1296,11 @@
           <t>Required</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
+      <c r="D11" s="18">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="12" ht="34.7" customHeight="1">
       <c r="A12" s="13" t="inlineStr">
         <is>
           <t>Reviewer (Role)</t>
@@ -1394,10 +1404,8 @@
           <t>Required</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>2027-03-01</t>
-        </is>
+      <c r="D16" s="18">
+        <v>46447</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -1475,6 +1483,7 @@
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="B23:D23"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>